--- a/debug/judgements_intro/excel_overviews/gpt-4.1_vs_gemini-1.5-flash/Mistral-7B-Instruct-v0.3/metrics_default_vs_simple.xlsx
+++ b/debug/judgements_intro/excel_overviews/gpt-4.1_vs_gemini-1.5-flash/Mistral-7B-Instruct-v0.3/metrics_default_vs_simple.xlsx
@@ -420,7 +420,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>0.4677419354838709</v>
+        <v>0.4259259259259259</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -429,16 +429,16 @@
         <v>0.676056338028169</v>
       </c>
       <c r="D2">
-        <v>0.6133333333333333</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="E2">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="F2">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G2">
-        <v>67</v>
+        <v>73</v>
       </c>
     </row>
   </sheetData>
